--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect &amp; IAM Data Modernization</t>
+          <t>Software Engineer II, Pricing Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a876f1d70bf86df</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2bac108848ff31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Engineer - Egypt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2bac108848ff31</t>
+          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Egypt</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,64 +556,64 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
+          <t>https://www.indeed.com/viewjob?jk=f422e5e1f7c77012</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer /Power BI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422e5e1f7c77012</t>
+          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer /Power BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
+          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4955bf068961211</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
+          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,112 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4955bf068961211</t>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Wayfair</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Data Engineer - Egypt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2bac108848ff31</t>
+          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Egypt</t>
+          <t>Data Engineer /Power BI Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422e5e1f7c77012</t>
+          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer /Power BI Developer</t>
+          <t>Senior Software Engineer (Java) in Test</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
+          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,77 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
+          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - Egypt</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,33 +482,33 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
+          <t>https://www.indeed.com/viewjob?jk=622e5174e22fc102</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer /Power BI Developer</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,33 +517,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
+          <t>https://www.indeed.com/viewjob?jk=239176039e388a7a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,46 +552,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac1dcfa7fd19426</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>Data Engineer - Egypt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Data Engineer /Power BI Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
         </is>
       </c>
     </row>
@@ -648,82 +648,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Java) in Test</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,15 +731,120 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
         </is>

--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Egypt</t>
+          <t>Referral Only - Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,29 +591,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
+          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer /Power BI Developer</t>
+          <t>Data Engineer - Egypt</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
+          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,91 +657,91 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>Full Stack Software Engineer @ Hybrid</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>NextRow Digital</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Data Engineer /Power BI Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
         </is>
       </c>
     </row>
@@ -753,82 +753,82 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Java) in Test</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,15 +836,155 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Middle–Senior Data Engineer with AI Experience</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
         </is>

--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622e5174e22fc102</t>
+          <t>https://www.indeed.com/viewjob?jk=c207b60a85c3ae78</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>AI Integration Specialist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Trauma Healing Accelerated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239176039e388a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7b42d068847f61</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Referral Only - Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac1dcfa7fd19426</t>
+          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Referral Only - Senior GCP Data Engineer</t>
+          <t>Data Engineer - Egypt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,29 +591,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Egypt</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Full Stack Software Engineer @ Hybrid</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>NextRow Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,64 +661,64 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer @ Hybrid</t>
+          <t>Data Engineer /Power BI Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NextRow Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
+          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer /Power BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
+          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Java) in Test</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Middle–Senior Data Engineer with AI Experience</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Middle–Senior Data Engineer with AI Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -950,41 +950,6 @@
         </is>
       </c>
       <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Vulcan Elements</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
         </is>

--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer /Power BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
+          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Java) in Test</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Middle–Senior Data Engineer with AI Experience</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Middle–Senior Data Engineer with AI Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -915,41 +915,6 @@
         </is>
       </c>
       <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Vulcan Elements</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
         </is>

--- a/results/job_matches_2026-05-25.xlsx
+++ b/results/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Referral Only - Senior GCP Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Egypt</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,33 +587,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,46 +622,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer @ Hybrid</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NextRow Digital</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,81 +692,81 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Middle–Senior Data Engineer with AI Experience</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,40 +881,355 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Referral Only - Senior GCP Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer - Egypt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Protagona</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c80b353eec9dd01f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Panasonic Automotive</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer @ Hybrid</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NextRow Digital</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Data Engineer</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Protagona</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer 5.5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Middle–Senior Data Engineer with AI Experience</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Vulcan Elements</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Durham, NC, US USA</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D23" t="n">
         <v>11.1</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
         </is>
